--- a/data/pack/uk/toros_ni.xlsx
+++ b/data/pack/uk/toros_ni.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K250"/>
+  <dimension ref="A1:K251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14184,6 +14184,61 @@
         </is>
       </c>
       <c r="K250" t="inlineStr">
+        <is>
+          <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: DAERA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>toros_ni</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Toros jóvenes, en canal (Irlanda del Norte)</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>6.129</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>DAERA (Northern Ireland) — Agricultural Market Report</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>OGL-UK-3.0</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
         <is>
           <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: DAERA.</t>
         </is>
@@ -14287,7 +14342,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14353,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">

--- a/data/pack/uk/toros_ni.xlsx
+++ b/data/pack/uk/toros_ni.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K251"/>
+  <dimension ref="A1:K252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14239,6 +14239,61 @@
         </is>
       </c>
       <c r="K251" t="inlineStr">
+        <is>
+          <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: DAERA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>toros_ni</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Toros jóvenes, en canal (Irlanda del Norte)</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>6.113</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>DAERA (Northern Ireland) — Agricultural Market Report</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>OGL-UK-3.0</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
         <is>
           <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: DAERA.</t>
         </is>
@@ -14342,7 +14397,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -14353,7 +14408,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
@@ -14448,7 +14503,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
